--- a/重点商品CA別進捗_2026年6月.xlsx
+++ b/重点商品CA別進捗_2026年6月.xlsx
@@ -16,13 +16,13 @@
     <sheet name="クエスト5・U-Car石川" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -213,7 +213,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -239,28 +239,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -287,21 +272,6 @@
               </pt>
               <pt idx="8">
                 <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -365,6 +335,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -415,7 +393,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -441,28 +419,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -488,21 +451,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
                 <v>0</v>
               </pt>
             </numLit>
@@ -567,6 +515,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -617,7 +573,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -637,19 +593,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -669,12 +619,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -739,6 +683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -789,7 +741,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -809,19 +761,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -841,12 +787,6 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -911,6 +851,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -961,7 +909,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -981,19 +929,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1014,12 +956,6 @@
               </pt>
               <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -1083,6 +1019,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1133,7 +1077,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1153,19 +1097,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1185,12 +1123,6 @@
                 <v>2</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1255,6 +1187,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1305,7 +1245,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1325,19 +1265,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -1357,13 +1291,7 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>2</v>
-              </pt>
-              <pt idx="8">
-                <v>1</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -1427,6 +1355,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1477,7 +1413,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1497,19 +1433,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -1529,12 +1459,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1599,6 +1523,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1649,7 +1581,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1669,19 +1601,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1701,12 +1627,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1771,6 +1691,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1821,7 +1749,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1841,19 +1769,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -1873,12 +1795,6 @@
                 <v>1</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1943,6 +1859,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1993,7 +1917,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2013,19 +1937,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2046,12 +1964,6 @@
               </pt>
               <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2115,6 +2027,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2165,7 +2085,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -2191,28 +2111,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -2238,22 +2143,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
                 <v>2</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2317,6 +2207,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2367,7 +2265,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2387,19 +2285,13 @@
                 <v>田中　智久</v>
               </pt>
               <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="8">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="9"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2419,12 +2311,6 @@
                 <v>0</v>
               </pt>
               <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
-              </pt>
-              <pt idx="8">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2489,6 +2375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2539,7 +2433,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2556,19 +2450,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -2586,12 +2474,6 @@
               </pt>
               <pt idx="5">
                 <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2655,6 +2537,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2705,7 +2595,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2722,19 +2612,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2751,13 +2635,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -2821,6 +2699,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2871,7 +2757,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -2888,19 +2774,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -2917,12 +2797,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>1</v>
               </pt>
             </numLit>
@@ -2987,6 +2861,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3037,7 +2919,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3054,19 +2936,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
@@ -3084,12 +2960,6 @@
               </pt>
               <pt idx="5">
                 <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -3153,6 +3023,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3203,7 +3081,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3220,19 +3098,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>6</v>
               </pt>
@@ -3249,13 +3121,7 @@
                 <v>5</v>
               </pt>
               <pt idx="5">
-                <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3319,6 +3185,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3369,7 +3243,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3386,19 +3260,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>4</v>
               </pt>
@@ -3416,12 +3284,6 @@
               </pt>
               <pt idx="5">
                 <v>1</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -3467,7 +3329,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="6"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3485,6 +3347,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3535,7 +3405,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3552,19 +3422,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -3581,12 +3445,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3651,6 +3509,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3701,7 +3567,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3718,19 +3584,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -3747,13 +3607,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>2</v>
-              </pt>
-              <pt idx="7">
-                <v>1</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -3799,7 +3653,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3817,6 +3671,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3867,7 +3729,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -3884,19 +3746,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -3913,13 +3769,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
                 <v>1</v>
-              </pt>
-              <pt idx="7">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -3983,6 +3833,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4033,7 +3891,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -4059,28 +3917,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4106,21 +3949,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4185,6 +4013,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4235,7 +4071,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>水嶋　規雄</v>
               </pt>
@@ -4252,19 +4088,13 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="6">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="7">
-                <v>阿部　隆二</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="8"/>
+              <ptCount val="6"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -4281,12 +4111,6 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>0</v>
-              </pt>
-              <pt idx="7">
                 <v>0</v>
               </pt>
             </numLit>
@@ -4351,6 +4175,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4412,7 +4244,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4493,6 +4325,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4554,7 +4394,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4635,6 +4475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4696,7 +4544,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4777,6 +4625,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4838,7 +4694,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4919,6 +4775,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4980,7 +4844,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5061,6 +4925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5122,7 +4994,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5203,6 +5075,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5264,7 +5144,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5345,6 +5225,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5406,7 +5294,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5487,6 +5375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5548,7 +5444,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5629,6 +5525,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5679,7 +5583,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -5705,28 +5609,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -5752,22 +5641,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>3</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
+                <v>5</v>
               </pt>
             </numLit>
           </val>
@@ -5813,7 +5687,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5831,6 +5705,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5892,7 +5774,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5973,6 +5855,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6031,7 +5921,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6109,6 +5999,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6167,7 +6065,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6227,7 +6125,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6245,6 +6143,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6303,7 +6209,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6381,6 +6287,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6439,7 +6353,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6517,6 +6431,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6575,7 +6497,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6653,6 +6575,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6711,7 +6641,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6771,7 +6701,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6789,6 +6719,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6847,7 +6785,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -6925,6 +6863,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6983,7 +6929,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7061,6 +7007,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7119,7 +7073,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7179,7 +7133,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7197,6 +7151,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7247,7 +7209,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -7273,28 +7235,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>11</v>
               </pt>
@@ -7320,22 +7267,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>5</v>
-              </pt>
-              <pt idx="9">
-                <v>3</v>
-              </pt>
-              <pt idx="10">
-                <v>2</v>
-              </pt>
-              <pt idx="11">
-                <v>5</v>
-              </pt>
-              <pt idx="12">
-                <v>5</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
+                <v>20</v>
               </pt>
             </numLit>
           </val>
@@ -7381,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="11"/>
+          <max val="20"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7399,6 +7331,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7457,7 +7397,7 @@
                 <v>赤平　恵一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7535,6 +7475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7593,7 +7541,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7671,6 +7619,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7729,7 +7685,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7789,7 +7745,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7807,6 +7763,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7865,7 +7829,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7925,7 +7889,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7943,6 +7907,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8001,7 +7973,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8079,6 +8051,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8137,7 +8117,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8197,7 +8177,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8215,6 +8195,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8273,7 +8261,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8333,7 +8321,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8351,6 +8339,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8409,7 +8405,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8487,6 +8483,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8545,7 +8549,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8623,6 +8627,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8681,7 +8693,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8759,6 +8771,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8809,7 +8829,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -8835,28 +8855,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
@@ -8882,22 +8887,7 @@
                 <v>1</v>
               </pt>
               <pt idx="8">
-                <v>2</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>4</v>
-              </pt>
-              <pt idx="13">
-                <v>1</v>
+                <v>8</v>
               </pt>
             </numLit>
           </val>
@@ -8961,6 +8951,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9019,7 +9017,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -9079,7 +9077,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -9097,6 +9095,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9236,6 +9242,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9375,6 +9389,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9514,6 +9536,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9653,6 +9683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9792,6 +9830,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9931,6 +9977,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10070,6 +10124,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10209,6 +10271,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10348,6 +10418,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10398,7 +10476,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10424,28 +10502,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -10471,21 +10534,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10550,6 +10598,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10689,6 +10745,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10739,7 +10803,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10765,28 +10829,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>8</v>
               </pt>
@@ -10813,21 +10862,6 @@
               </pt>
               <pt idx="8">
                 <v>4</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -10891,6 +10925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10941,7 +10983,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10967,28 +11009,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>秋山　泰賢</v>
-              </pt>
-              <pt idx="11">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
-              </pt>
-              <pt idx="13">
-                <v>前野　正樹</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="14"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -11014,22 +11041,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>1</v>
-              </pt>
-              <pt idx="13">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -11093,6 +11105,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -11105,7 +11125,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11127,7 +11147,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11149,7 +11169,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11171,7 +11191,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11193,7 +11213,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11215,7 +11235,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11237,7 +11257,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11259,7 +11279,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11281,7 +11301,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11303,7 +11323,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11330,7 +11350,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11352,7 +11372,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11374,7 +11394,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11396,7 +11416,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11418,7 +11438,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11440,7 +11460,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11462,7 +11482,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11484,7 +11504,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11506,7 +11526,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11528,7 +11548,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11555,7 +11575,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11577,7 +11597,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11599,7 +11619,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11621,7 +11641,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11643,7 +11663,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11665,7 +11685,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11687,7 +11707,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11709,7 +11729,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11731,7 +11751,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11753,7 +11773,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11780,7 +11800,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11802,7 +11822,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11824,7 +11844,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11846,7 +11866,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11868,7 +11888,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11890,7 +11910,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11912,7 +11932,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11934,7 +11954,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11956,7 +11976,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11978,7 +11998,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12005,7 +12025,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12027,7 +12047,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12049,7 +12069,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12071,7 +12091,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12093,7 +12113,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12115,7 +12135,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12137,7 +12157,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12159,7 +12179,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12181,7 +12201,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12203,7 +12223,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12230,7 +12250,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12252,7 +12272,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12274,7 +12294,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12296,7 +12316,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12318,7 +12338,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12340,7 +12360,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12362,7 +12382,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12384,7 +12404,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12406,7 +12426,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12428,7 +12448,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12455,7 +12475,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12477,7 +12497,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12499,7 +12519,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12521,7 +12541,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12543,7 +12563,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12565,7 +12585,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12587,7 +12607,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12609,7 +12629,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12631,7 +12651,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12653,7 +12673,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12960,663 +12980,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42.48" customWidth="1" min="1" max="1"/>
-    <col width="42.48" customWidth="1" min="2" max="2"/>
-    <col width="42.48" customWidth="1" min="3" max="3"/>
-    <col width="42.48" customWidth="1" min="4" max="4"/>
-    <col width="42.48" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="9" customWidth="1" min="22" max="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">石川店 CA別進捗(重点10商品) </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>商品名</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>加
-藤
-英
-基</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>川
-村
-正
-敏</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>村
-上
-英
-俊</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>阿
-部
-隆
-二</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>野
-呂
-藍
-亮</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>小
-野
-翼</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>橋
-本
-隆
-志</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>岩
-坪
-公
-夫</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>鈴
-木
-聡</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>秋
-山
-泰
-賢</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>落
-合
-典
-彦</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>石
-澤
-直
-道</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>前
-野
-正
-樹</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>エンジンリフレッシュ</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>エアコン潤滑剤 NC200マキシクール</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>ウィンドウ撥水12カ月</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>エアコン/ヒーター洗浄12カ月</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Ｆ-Premium</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>クーラントエナジー</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>抗菌・抗ウィルスコート</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>ボディーコート3カ月</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>NISMOオイル / Mobil1オイル （台数）</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>ギヤボックス添加剤　SuperADD1201</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13640,12 +13003,12 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">亀本店 CA別進捗(重点10商品) </t>
+          <t xml:space="preserve">石川店 CA別進捗(重点10商品) </t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -13653,135 +13016,132 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>大
-島
-貞
-男</t>
+          <t>加
+藤
+英
+基</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>杉
-澤
-修
-平</t>
+          <t>川
+村
+正
+敏</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>平
-館
-健</t>
+          <t>村
+上
+英
+俊</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>平
-賀
-崇</t>
+          <t>阿
+部
+隆
+二</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>安
-部
-雅
-史</t>
+          <t>野
+呂
+藍
+亮</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>田
-中
-智
-久</t>
+          <t>小
+野
+翼</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>橋
+本
+隆
+志</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>鈴
-木
-聡</t>
+          <t>岩
+坪
+公
+夫</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>前
-野
-正
-樹</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="4" t="n">
         <v>0</v>
@@ -13790,10 +13150,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -13806,19 +13166,19 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="4" t="n">
         <v>0</v>
@@ -13827,29 +13187,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O7" s="4" t="n">
         <v>0</v>
@@ -13858,41 +13218,41 @@
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" s="4" t="n">
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N8" s="4" t="n">
+      <c r="P8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -13902,31 +13262,31 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -13936,13 +13296,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="4" t="n">
         <v>0</v>
@@ -13970,31 +13330,31 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" s="4" t="n">
+      <c r="Q11" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14004,31 +13364,31 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14044,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>0</v>
@@ -14066,19 +13426,20 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -14094,7 +13455,385 @@
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亀本店 CA別進捗(重点10商品) </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="358.5826771653543" customHeight="1">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>商品名</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>大
+島
+貞
+男</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>杉
+澤
+修
+平</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>平
+館
+健</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>平
+賀
+崇</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>安
+部
+雅
+史</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>田
+中
+智
+久</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42.51968503937007" customHeight="1">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>エンジンリフレッシュ</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="358.5826771653543" customHeight="1">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>エアコン潤滑剤 NC200マキシクール</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>ウィンドウ撥水12カ月</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>エアコン/ヒーター洗浄12カ月</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Ｆ-Premium</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>クーラントエナジー</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>抗菌・抗ウィルスコート</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>ボディーコート3カ月</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>NISMOオイル / Mobil1オイル （台数）</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>ギヤボックス添加剤　SuperADD1201</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
+  <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42.48" customWidth="1" min="1" max="1"/>
+    <col width="42.48" customWidth="1" min="2" max="2"/>
+    <col width="42.48" customWidth="1" min="3" max="3"/>
+    <col width="42.48" customWidth="1" min="4" max="4"/>
+    <col width="42.48" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -14105,7 +13844,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14152,34 +13891,13 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>落
-合
-典
-彦</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>阿
-部
-隆
-二</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14203,14 +13921,8 @@
       <c r="N4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14232,16 +13944,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14263,16 +13969,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14296,14 +13996,8 @@
       <c r="N7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -14325,13 +14019,7 @@
         <v>5</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -14358,12 +14046,6 @@
       <c r="N9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -14389,12 +14071,6 @@
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -14418,13 +14094,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -14449,13 +14119,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14482,14 +14146,9 @@
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14525,7 +14184,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14558,18 +14217,13 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14588,7 +14242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14607,7 +14261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14626,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14645,7 +14299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -14760,6 +14414,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14794,7 +14449,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14818,18 +14473,13 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14845,7 +14495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14861,7 +14511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14877,7 +14527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14893,7 +14543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -14990,6 +14640,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15024,7 +14675,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15048,18 +14699,13 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15075,7 +14721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15091,7 +14737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15107,7 +14753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15123,7 +14769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -15220,6 +14866,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -15256,7 +14903,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -15302,7 +14949,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -15324,7 +14971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -15346,7 +14993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -15368,7 +15015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -15390,7 +15037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ｆ-Premium</t>
@@ -15523,6 +15170,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
